--- a/internal_doc/05.测试设计/story/Sequence&AutoIncrement/异常.xlsx
+++ b/internal_doc/05.测试设计/story/Sequence&AutoIncrement/异常.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>name</t>
   </si>
@@ -128,10 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不指定自增字段插入时catalog主节点异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不指定自增字段插入时coord主节点异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -179,53 +175,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>集合中已存在自增字段且存在记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新记录，自增字段值保留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.使用replace更新符更新记录，覆盖：更新前记录无自增字段、更新前记录存在自增字段
-2.使用其他操作符更新记录，覆盖：更新其他字段、记录新增自增字段、记录删除自增字段、更新自增字段值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.记录更新成功，更新记录不会修改自增字段
-2.记录更新成功，更新记录系统不会生成自增字段值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自增字段同时是shardKey时，更新记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.删除记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.记录删除成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>truncate集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.truncate集合
-2.连本coord插入记录
-3.连其他coord插入记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.集合truncate成功，检查自增字段属性值CurrentValue值为StartValue
-2.本地coord的sequence缓存被清空，重新从catalog获取新的序列值插入记录
-3.其他coord的sequence缓存被清空，重新从catalog获取新的序列值插入记录</t>
+    <t>不指定自增字段插入时catalog主节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CacheSize及AcquireSize均设置为1，不指定自增字段插入时catalog主节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CacheSize及AcquireSize均设置为1，不指定自增字段插入时coord主节点异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -269,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -281,9 +239,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -375,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I15" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I11" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -695,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -886,10 +841,10 @@
     </row>
     <row r="8" spans="1:9" ht="54">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -901,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" s="3">
         <v>2</v>
@@ -912,10 +867,10 @@
     </row>
     <row r="9" spans="1:9" ht="54">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -927,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="I9" s="3">
         <v>2</v>
@@ -938,10 +893,10 @@
     </row>
     <row r="10" spans="1:9" ht="40.5">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -953,10 +908,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="I10" s="3">
         <v>2</v>
@@ -964,11 +919,11 @@
     </row>
     <row r="11" spans="1:9" ht="40.5">
       <c r="A11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D11" s="3">
         <v>2</v>
       </c>
@@ -979,119 +934,12 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I11" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="54">
-      <c r="A12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="54">
-      <c r="A13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="27">
-      <c r="A14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="81">
-      <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="3">
-        <v>2</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="3">
         <v>2</v>
       </c>
     </row>
